--- a/Replication/simulations.xlsx
+++ b/Replication/simulations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <si>
     <t xml:space="preserve">betal_OLS</t>
   </si>
@@ -68,148 +68,433 @@
     <t xml:space="preserve">gamma:GX2_RF</t>
   </si>
   <si>
+    <t xml:space="preserve">beta_SYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma:X1_SYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma:X2_SYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma:GX1_SYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma:GX2_SYM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rho_CES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta_CES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X1_CES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X2_CES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GX1_CES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GX2_CES</t>
+  </si>
+  <si>
     <t xml:space="preserve">DGP A: $\boldsymbol\beta^l = (1)$, $\beta^h = 1$</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">1.020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.199</t>
+    <t xml:space="preserve">1.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.080)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.077)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.029)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.084)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.069)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.391)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.071)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGP B: $\boldsymbol\beta^l = (2)$, $\beta^h = 1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.137)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.105)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.134)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.099)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.143)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.109)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.619)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGP C: $\boldsymbol\beta^l = (1)$, $\beta^h = 2$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.196</t>
   </si>
   <si>
     <t xml:space="preserve">0.600</t>
   </si>
   <si>
-    <t xml:space="preserve">1.021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.055)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.065)</t>
+    <t xml:space="preserve">(0.058)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.129)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.116)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.081)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.062)</t>
   </si>
   <si>
     <t xml:space="preserve">(0.014)</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.019)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.056)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.064)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.015)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.057)</t>
+    <t xml:space="preserve">(0.469)</t>
   </si>
   <si>
     <t xml:space="preserve">(0.068)</t>
   </si>
   <si>
-    <t xml:space="preserve">DGP B: $\boldsymbol\beta^l = (2)$, $\beta^h = 1$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.079)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.017)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.080)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGP C: $\boldsymbol\beta^l = (1)$, $\beta^h = 2$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.054)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.091)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.086)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.088)</t>
+    <t xml:space="preserve">(0.008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGP D: $\boldsymbol\beta^l = (1)$, $\beta^h = 1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.107)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.093)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.436)</t>
   </si>
 </sst>
 </file>
@@ -593,509 +878,1106 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="R2" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>29</v>
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="Q4" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="R4" t="s">
-        <v>38</v>
+        <v>57</v>
+      </c>
+      <c r="S4" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
+        <v>61</v>
+      </c>
+      <c r="W4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="R5" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="S5" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" t="s">
+        <v>30</v>
+      </c>
+      <c r="V5" t="s">
+        <v>30</v>
+      </c>
+      <c r="W5" t="s">
+        <v>30</v>
+      </c>
+      <c r="X5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6" t="s">
+        <v>76</v>
+      </c>
+      <c r="O6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" t="s">
+        <v>72</v>
+      </c>
+      <c r="S6" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" t="s">
+        <v>78</v>
+      </c>
+      <c r="U6" t="s">
+        <v>79</v>
+      </c>
+      <c r="V6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB6" t="s">
         <v>48</v>
       </c>
-      <c r="H6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" t="s">
-        <v>29</v>
+      <c r="AC6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" t="s">
         <v>54</v>
       </c>
-      <c r="J7" t="s">
-        <v>39</v>
-      </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="O7" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="Q7" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="R7" t="s">
-        <v>38</v>
+        <v>57</v>
+      </c>
+      <c r="S7" t="s">
+        <v>95</v>
+      </c>
+      <c r="T7" t="s">
+        <v>96</v>
+      </c>
+      <c r="U7" t="s">
+        <v>54</v>
+      </c>
+      <c r="V7" t="s">
+        <v>89</v>
+      </c>
+      <c r="W7" t="s">
+        <v>54</v>
+      </c>
+      <c r="X7" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="R8" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="S8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" t="s">
+        <v>30</v>
+      </c>
+      <c r="V8" t="s">
+        <v>30</v>
+      </c>
+      <c r="W8" t="s">
+        <v>30</v>
+      </c>
+      <c r="X8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="O9" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="P9" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="Q9" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="R9" t="s">
-        <v>25</v>
+        <v>108</v>
+      </c>
+      <c r="S9" t="s">
+        <v>113</v>
+      </c>
+      <c r="T9" t="s">
+        <v>114</v>
+      </c>
+      <c r="U9" t="s">
+        <v>115</v>
+      </c>
+      <c r="V9" t="s">
+        <v>116</v>
+      </c>
+      <c r="W9" t="s">
+        <v>117</v>
+      </c>
+      <c r="X9" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
         <v>61</v>
       </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="G10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
+        <v>127</v>
+      </c>
+      <c r="M10" t="s">
+        <v>130</v>
+      </c>
+      <c r="N10" t="s">
+        <v>125</v>
+      </c>
+      <c r="O10" t="s">
+        <v>126</v>
+      </c>
+      <c r="P10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>101</v>
+      </c>
+      <c r="R10" t="s">
+        <v>127</v>
+      </c>
+      <c r="S10" t="s">
+        <v>131</v>
+      </c>
+      <c r="T10" t="s">
+        <v>132</v>
+      </c>
+      <c r="U10" t="s">
+        <v>96</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>51</v>
+      </c>
+      <c r="X10" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" t="s">
+        <v>30</v>
+      </c>
+      <c r="S11" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" t="s">
+        <v>30</v>
+      </c>
+      <c r="U11" t="s">
+        <v>30</v>
+      </c>
+      <c r="V11" t="s">
+        <v>30</v>
+      </c>
+      <c r="W11" t="s">
+        <v>30</v>
+      </c>
+      <c r="X11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" t="s">
+        <v>141</v>
+      </c>
+      <c r="L12" t="s">
+        <v>142</v>
+      </c>
+      <c r="M12" t="s">
+        <v>145</v>
+      </c>
+      <c r="N12" t="s">
+        <v>146</v>
+      </c>
+      <c r="O12" t="s">
+        <v>139</v>
+      </c>
+      <c r="P12" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>141</v>
+      </c>
+      <c r="R12" t="s">
+        <v>147</v>
+      </c>
+      <c r="S12" t="s">
+        <v>148</v>
+      </c>
+      <c r="T12" t="s">
+        <v>149</v>
+      </c>
+      <c r="U12" t="s">
+        <v>85</v>
+      </c>
+      <c r="V12" t="s">
+        <v>150</v>
+      </c>
+      <c r="W12" t="s">
+        <v>117</v>
+      </c>
+      <c r="X12" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" t="s">
+        <v>156</v>
+      </c>
+      <c r="G13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H13" t="s">
         <v>63</v>
       </c>
-      <c r="H10" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O10" t="s">
-        <v>42</v>
-      </c>
-      <c r="P10" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>37</v>
-      </c>
-      <c r="R10" t="s">
-        <v>38</v>
+      <c r="I13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" t="s">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s">
+        <v>94</v>
+      </c>
+      <c r="N13" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" t="s">
+        <v>156</v>
+      </c>
+      <c r="P13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>90</v>
+      </c>
+      <c r="R13" t="s">
+        <v>156</v>
+      </c>
+      <c r="S13" t="s">
+        <v>159</v>
+      </c>
+      <c r="T13" t="s">
+        <v>101</v>
+      </c>
+      <c r="U13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V13" t="s">
+        <v>89</v>
+      </c>
+      <c r="W13" t="s">
+        <v>156</v>
+      </c>
+      <c r="X13" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
